--- a/Gistda_Price_List_structured.xlsx
+++ b/Gistda_Price_List_structured.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>satellite</t>
+          <t>name</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -451,19 +451,29 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>archive_price</t>
+          <t>price_1_label</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>tasking_price</t>
+          <t>price_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>price_2_label</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>price_2</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูงมาก</t>
+          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูงมาก (รายละเอียดภาพ 30 – 50 ซม.)</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -481,10 +491,20 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>880</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>1,270</t>
         </is>
@@ -493,7 +513,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูงมาก</t>
+          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูงมาก (รายละเอียดภาพ 30 – 50 ซม.)</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -511,10 +531,20 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>920</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>1,560</t>
         </is>
@@ -523,7 +553,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูงมาก</t>
+          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูงมาก (รายละเอียดภาพ 30 – 50 ซม.)</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -541,10 +571,20 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>700</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>1,100</t>
         </is>
@@ -553,7 +593,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูงมาก</t>
+          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูงมาก (รายละเอียดภาพ 30 – 50 ซม.)</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -571,10 +611,20 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>700</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>1,100</t>
         </is>
@@ -583,7 +633,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูงมาก</t>
+          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูงมาก (รายละเอียดภาพ 30 – 50 ซม.)</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -601,10 +651,20 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>700</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>1,100</t>
         </is>
@@ -613,7 +673,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูงมาก</t>
+          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูงมาก (รายละเอียดภาพ 30 – 50 ซม.)</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -631,10 +691,20 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>700</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>1,100</t>
         </is>
@@ -643,7 +713,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูงมาก</t>
+          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูงมาก (รายละเอียดภาพ 30 – 50 ซม.)</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -661,10 +731,20 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>700</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t>1,100</t>
         </is>
@@ -673,7 +753,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูงมาก</t>
+          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูงมาก (รายละเอียดภาพ 30 – 50 ซม.)</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -691,10 +771,20 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>490</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t>830</t>
         </is>
@@ -703,7 +793,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูงมาก</t>
+          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูงมาก (รายละเอียดภาพ 30 – 50 ซม.)</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -721,10 +811,20 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>400</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
         <is>
           <t>800</t>
         </is>
@@ -733,7 +833,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูงมาก</t>
+          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูงมาก (รายละเอียดภาพ 30 – 50 ซม.)</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -751,10 +851,20 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>500</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
         <is>
           <t>900</t>
         </is>
@@ -763,7 +873,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูงมาก</t>
+          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูงมาก (รายละเอียดภาพ 30 – 50 ซม.)</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -781,10 +891,20 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>400</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
         <is>
           <t>700</t>
         </is>
@@ -793,7 +913,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูงมาก</t>
+          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูงมาก (รายละเอียดภาพ 30 – 50 ซม.)</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -811,10 +931,20 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
           <t>300</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>560</t>
         </is>
@@ -823,7 +953,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูง</t>
+          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูง (รายละเอียดภาพ 60 ซม. – 2 ม.)</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -831,29 +961,35 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Video Constellation</t>
+          <t>QuickBird</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1 m.</t>
+          <t>60 cm.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>142,500</t>
+          <t>Archive</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>285,000</t>
-        </is>
-      </c>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูง</t>
+          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูง (รายละเอียดภาพ 60 ซม. – 2 ม.)</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -861,29 +997,39 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Night Imaging</t>
+          <t>GaoFen-7</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1 m.</t>
+          <t>65 cm.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>Archive</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1,400</t>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>700</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูง</t>
+          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูง (รายละเอียดภาพ 60 ซม. – 2 ม.)</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -891,25 +1037,39 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>QuickBird</t>
+          <t>Jilin</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>60 cm.</t>
+          <t>75 cm.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูง</t>
+          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูง (รายละเอียดภาพ 60 ซม. – 2 ม.)</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -917,29 +1077,39 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GaoFen-7</t>
+          <t>DailyVision</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>65 cm.</t>
+          <t>75 cm.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>Archive</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>600</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูง</t>
+          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูง (รายละเอียดภาพ 60 ซม. – 2 ม.)</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -947,29 +1117,39 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jilin</t>
+          <t>GaoFen-2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>75 cm.</t>
+          <t>80 cm.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t>300</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>600</t>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>400</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูง</t>
+          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูง (รายละเอียดภาพ 60 ซม. – 2 ม.)</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -977,29 +1157,35 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DailyVision</t>
+          <t>IKONOS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>75 cm.</t>
+          <t>1 m.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>Archive</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>600</t>
-        </is>
-      </c>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูง</t>
+          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูง (รายละเอียดภาพ 60 ซม. – 2 ม.)</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1007,29 +1193,39 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GaoFen-2</t>
+          <t>Video Constellation</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>80 cm.</t>
+          <t>1 m.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>Archive</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>142,500</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>285,000</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูง</t>
+          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดสูง (รายละเอียดภาพ 60 ซม. – 2 ม.)</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1037,7 +1233,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>IKONOS</t>
+          <t>Night Imaging</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1047,10 +1243,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>1,400</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1063,22 +1273,32 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ไทยโชต</t>
+          <t>SPOT-6</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2 m.</t>
+          <t>1.5 m.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>700</t>
+          <t>Archive</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>6,500</t>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>230</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1313,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SPOT-6</t>
+          <t>SPOT-7</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1103,10 +1323,20 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
         <is>
           <t>230</t>
         </is>
@@ -1123,29 +1353,39 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SPOT-7</t>
+          <t>ไทยโชต</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.5 m.</t>
+          <t>2 m.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>190</t>
+          <t>Archive</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>6,500</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดปานกลาง</t>
+          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดปานกลาง (รายละเอียดมากกว่า 2 เมตร)</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1163,15 +1403,25 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>150</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดปานกลาง</t>
+          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดปานกลาง (รายละเอียดมากกว่า 2 เมตร)</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1189,15 +1439,25 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
           <t>150</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดปานกลาง</t>
+          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดปานกลาง (รายละเอียดมากกว่า 2 เมตร)</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1215,15 +1475,25 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>150</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดปานกลาง</t>
+          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดปานกลาง (รายละเอียดมากกว่า 2 เมตร)</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1241,15 +1511,25 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>150</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดปานกลาง</t>
+          <t>ราคาข้อมูลจากดาวเทียมรายละเอียดปานกลาง (รายละเอียดมากกว่า 2 เมตร)</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1257,20 +1537,30 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>PLANETSCOPE 3 m.</t>
+          <t>PLANETSCOPE Access+Download</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Access+Download</t>
+          <t>3 m.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
         <is>
           <t>240</t>
         </is>
@@ -1287,7 +1577,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Standard</t>
+          <t>RADARSAT-2 (C band) - Standard</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1297,10 +1587,20 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
+          <t>Single Look complex</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
           <t>57,600</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Path Image</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
         <is>
           <t>57,600</t>
         </is>
@@ -1317,7 +1617,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spotlight A</t>
+          <t>RADARSAT-2 (C band) - Spotlight A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1327,10 +1627,20 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>Single Look complex</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
           <t>134,400</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Path Image</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
         <is>
           <t>134,400</t>
         </is>
@@ -1347,7 +1657,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Utra-Fine</t>
+          <t>RADARSAT-2 (C band) - Utra-Fine</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1357,10 +1667,20 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
+          <t>Single Look complex</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>86,400</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Path Image</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
         <is>
           <t>86,400</t>
         </is>
@@ -1377,7 +1697,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Wide Utra-Fine</t>
+          <t>RADARSAT-2 (C band) - Wide Utra-Fine</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1387,10 +1707,20 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>Single Look complex</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t>124,800</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Path Image</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
         <is>
           <t>124,800</t>
         </is>
@@ -1407,7 +1737,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Multi-Look Fine</t>
+          <t>RADARSAT-2 (C band) - Multi-Look Fine</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1417,10 +1747,20 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t>Single Look complex</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t>67,200</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Path Image</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
         <is>
           <t>67,200</t>
         </is>
@@ -1437,7 +1777,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Wide Multi-Look Fine</t>
+          <t>RADARSAT-2 (C band) - Wide Multi-Look Fine</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1447,10 +1787,20 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
+          <t>Single Look complex</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t>120,000</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Path Image</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
         <is>
           <t>120,000</t>
         </is>
@@ -1467,7 +1817,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Fine</t>
+          <t>RADARSAT-2 (C band) - Fine</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1477,10 +1827,20 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
+          <t>Single Look complex</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
           <t>57,600</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Path Image</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
         <is>
           <t>57,600</t>
         </is>
@@ -1497,7 +1857,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Wide</t>
+          <t>RADARSAT-2 (C band) - Wide</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1507,10 +1867,20 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
+          <t>Single Look complex</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t>57,600</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Path Image</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
         <is>
           <t>57,600</t>
         </is>
@@ -1527,7 +1897,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ScanSAR Narrow</t>
+          <t>RADARSAT-2 (C band) - ScanSAR Narrow</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1535,8 +1905,18 @@
           <t>50 m.</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Single Look complex</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Path Image</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
         <is>
           <t>57,600</t>
         </is>
@@ -1553,7 +1933,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ScanSAR Wide</t>
+          <t>RADARSAT-2 (C band) - ScanSAR Wide</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1561,8 +1941,18 @@
           <t>100 m.</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr">
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Single Look complex</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Path Image</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
         <is>
           <t>57,600</t>
         </is>
@@ -1579,7 +1969,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Extended High, Low</t>
+          <t>RADARSAT-2 (C band) - Extended High, Low</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1589,10 +1979,20 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
+          <t>Single Look complex</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
           <t>57,600</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Path Image</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
         <is>
           <t>57,600</t>
         </is>
@@ -1609,7 +2009,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Fine Quad-Pol</t>
+          <t>RADARSAT-2 (C band) - Fine Quad-Pol</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1619,10 +2019,20 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
+          <t>Single Look complex</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
           <t>86,400</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Path Image</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1635,7 +2045,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Wide Fine Quad-Pol</t>
+          <t>RADARSAT-2 (C band) - Wide Fine Quad-Pol</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1645,10 +2055,20 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
+          <t>Single Look complex</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
           <t>124,800</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Path Image</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1661,7 +2081,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Staring Spotlight (ST)</t>
+          <t>TerraSar X (X band) - Staring Spotlight (ST)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1671,10 +2091,20 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t>162,630</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
         <is>
           <t>325,260</t>
         </is>
@@ -1691,7 +2121,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>High Res Spotlight (HS)</t>
+          <t>TerraSar X (X band) - High Res Spotlight (HS)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1701,10 +2131,20 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
           <t>139,230</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
         <is>
           <t>278,460</t>
         </is>
@@ -1721,7 +2161,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spotlight</t>
+          <t>TerraSar X (X band) - Spotlight</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1731,10 +2171,20 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
           <t>99,450</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
         <is>
           <t>198,900</t>
         </is>
@@ -1751,7 +2201,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>StripMap</t>
+          <t>TerraSar X (X band) - StripMap</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1761,10 +2211,20 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
           <t>69,030</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
         <is>
           <t>138,060</t>
         </is>
@@ -1781,7 +2241,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ScanSAR</t>
+          <t>TerraSar X (X band) - ScanSAR</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1791,10 +2251,20 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
           <t>40,950</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
         <is>
           <t>81,900</t>
         </is>
@@ -1811,7 +2281,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Wide ScanSAR</t>
+          <t>TerraSar X (X band) - Wide ScanSAR</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1821,10 +2291,20 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
+          <t>Archive</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
           <t>40,950</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
         <is>
           <t>81,900</t>
         </is>
@@ -1837,26 +2317,36 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>StripMap Himage 3 x 3 – 5</t>
+          <t>GaoFen-3 (C band) - Spotlight (SL) HH, VV</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>1 m.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Archive</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>93,000</t>
+          <t>116,400</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>180,500</t>
         </is>
       </c>
     </row>
@@ -1867,26 +2357,36 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>StripMap PingPong 10 x 12 – 20</t>
+          <t>GaoFen-3 (C band) - Ultra-fine Stripmap (UFS) HH, VV</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>3 m.</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>Archive</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>68,900</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>118,800</t>
         </is>
       </c>
     </row>
@@ -1897,26 +2397,36 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ScanSAR Wide 14 x 22 – 30</t>
+          <t>GaoFen-3 (C band) - Fine Stripmap (FSI) HH, VV</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>5 m.</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>Archive</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>78,000</t>
+          <t>64,200</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>95,000</t>
         </is>
       </c>
     </row>
@@ -1927,26 +2437,36 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ScanSAR Huge 14 x 38 – 100</t>
+          <t>GaoFen-3 (C band) - Wide Fine Stripmap (FSII) HH, HV / VV, VH</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>10 m.</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>Archive</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>78,000</t>
+          <t>64,200</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>90,300</t>
         </is>
       </c>
     </row>
@@ -1961,22 +2481,32 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spotlight (SL) 1 m. HH,</t>
+          <t>GaoFen-3 (C band) - Standard Stripmap (SS) HH, HV / VV, VH</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VV</t>
+          <t>25 m.</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>116,400</t>
+          <t>Archive</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>180,500</t>
+          <t>54,700</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>85,500</t>
         </is>
       </c>
     </row>
@@ -1991,22 +2521,32 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ultra-fine Stripmap (UFS) 3 m. HH,</t>
+          <t>GaoFen-3 (C band) - Narrow ScanSAR (NSC) HH, HV / VV, VH</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VV</t>
+          <t>50 m.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>68,900</t>
+          <t>Archive</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>118,800</t>
+          <t>32,100</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>42,800</t>
         </is>
       </c>
     </row>
@@ -2021,22 +2561,32 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Fine Stripmap (FSI) 5 m. HH,</t>
+          <t>GaoFen-3 (C band) - Wide ScanSAR (WSC) HH, HV / VV, VH</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VV</t>
+          <t>100 m.</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>64,200</t>
+          <t>Archive</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>95,000</t>
+          <t>32,100</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>45,800</t>
         </is>
       </c>
     </row>
@@ -2051,22 +2601,32 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Wide Fine Stripmap (FSII) 10 m. HH, HV / VV,</t>
+          <t>GaoFen-3 (C band) - Quad-pol Stripmap (QPSI) HH, HV / VV, VH</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VH</t>
+          <t>8 m.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>64,200</t>
+          <t>Archive</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>90,300</t>
+          <t>71,300</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>137,800</t>
         </is>
       </c>
     </row>
@@ -2081,22 +2641,32 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Standard Stripmap (SS) 25 m. HH, HV / VV,</t>
+          <t>GaoFen-3 (C band) - Wide Quad-pol Stripmap (QPSII) HH, HV / VV, VH</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VH</t>
+          <t>25 m.</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>54,700</t>
+          <t>Archive</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>85,500</t>
+          <t>71,300</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>137,800</t>
         </is>
       </c>
     </row>
@@ -2111,22 +2681,32 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Narrow ScanSAR (NSC) 50 m. HH, HV / VV,</t>
+          <t>GaoFen-3 (C band) - Wave (WAV) HH, HV / VV, VH</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VH</t>
+          <t>10 m.</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>32,100</t>
+          <t>Archive</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>42,800</t>
+          <t>10,700</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>14,300</t>
         </is>
       </c>
     </row>
@@ -2141,22 +2721,32 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Wide ScanSAR (WSC) 100 m. HH, HV / VV,</t>
+          <t>GaoFen-3 (C band) - Global Observation (GLO) HH, HV / VV, VH</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VH</t>
+          <t>500 m.</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>32,100</t>
+          <t>Archive</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>45,800</t>
+          <t>10,700</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>14,300</t>
         </is>
       </c>
     </row>
@@ -2171,140 +2761,30 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Quad-pol Stripmap (QPSI) 8 m. HH, HV / VV,</t>
+          <t>GaoFen-3 (C band) - Extended Incidence Angle (EXT) HH, HV / VV, VH</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VH</t>
+          <t>25 m.</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>71,300</t>
+          <t>Archive</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>137,800</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>ราคาข้อมูลจากดาวเทียมระบบเรดาร์</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>7</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Wide Quad-pol Stripmap (QPSII) 25 m. HH, HV / VV,</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>VH</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>71,300</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>137,800</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>ราคาข้อมูลจากดาวเทียมระบบเรดาร์</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>7</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Wave (WAV) 10 m. HH, HV / VV,</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>VH</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>10,700</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>14,300</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>ราคาข้อมูลจากดาวเทียมระบบเรดาร์</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>7</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Global Observation (GLO) 500 m. HH, HV / VV,</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>VH</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>10,700</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>14,300</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>ราคาข้อมูลจากดาวเทียมระบบเรดาร์</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>7</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Extended Incidence Angle (EXT) 25 m. HH, HV / VV,</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>VH</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
           <t>42,800</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Tasking</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
         <is>
           <t>57,000</t>
         </is>
